--- a/complaint_forms/033_student_complaint_form--complaint_forms.xlsx
+++ b/complaint_forms/033_student_complaint_form--complaint_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'academic_issue',_'value':_'academic_issue'}</t>
+          <t>academic_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Academic Issue', 'value': 'Academic Issue'}</t>
+          <t>Academic Issue</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'student_issue',_'value':_'student_issue'}</t>
+          <t>student_issue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Student Issue', 'value': 'Student Issue'}</t>
+          <t>Student Issue</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'faculty_issue',_'value':_'faculty_issue'}</t>
+          <t>faculty_issue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Faculty Issue', 'value': 'Faculty Issue'}</t>
+          <t>Faculty Issue</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit',_'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'submit', 'value': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'save_draft',_'value':_'save_draft'}</t>
+          <t>save_draft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Save Draft', 'value': 'Save Draft'}</t>
+          <t>Save Draft</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancel',_'value':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cancel', 'value': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'academic',_'value':_'academic'}</t>
+          <t>academic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Academic', 'value': 'Academic'}</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'administrative',_'value':_'administrative'}</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Administrative', 'value': 'Administrative'}</t>
+          <t>Administrative</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'academic',_'value':_'academic'}</t>
+          <t>academic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Academic', 'value': 'Academic'}</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'administrative',_'value':_'administrative'}</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Administrative', 'value': 'Administrative'}</t>
+          <t>Administrative</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
